--- a/research/CSW-Research-Database.xlsx
+++ b/research/CSW-Research-Database.xlsx
@@ -22,12 +22,12 @@
     <sheet name="» CSW_LOG" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'INBOX'!$A$2:$S$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'INBOX'!$A$2:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'OPERATORS'!$A$2:$U$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BRANDS'!$A$2:$O$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LOCATIONS'!$A$2:$V$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PEOPLE'!$A$2:$P$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'EVENTS'!$A$2:$Q$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'EVENTS'!$A$2:$R$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'SOURCES'!$A$2:$N$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'FDD_ROSTER'!$A$2:$S$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FDD_UNITS'!$A$2:$R$3</definedName>
@@ -1529,7 +1529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1545,18 +1545,19 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="52" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="52" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>PUT EVERYTHING HERE. Fill what you know, leave the rest blank. A sentence and a link is a valid row. Do not look anything up first — matching, de-duplicating and filing is done later, by me.</t>
+          <t>PUT EVERYTHING HERE. Fill what you know, leave the rest blank — a sentence and a link is a valid row. Nothing leaves this tab until you set ready = yes, so be as sloppy as you like everywhere else.</t>
         </is>
       </c>
     </row>
@@ -1628,30 +1629,35 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
           <t>entity_type</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="P2" s="8" t="inlineStr">
+      <c r="Q2" s="8" t="inlineStr">
         <is>
           <t>» row_id</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="inlineStr">
+      <c r="R2" s="8" t="inlineStr">
         <is>
           <t>» op_id</t>
         </is>
       </c>
-      <c r="R2" s="8" t="inlineStr">
+      <c r="S2" s="8" t="inlineStr">
         <is>
           <t>» csw_status</t>
         </is>
       </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>» csw_note</t>
         </is>
@@ -1721,33 +1727,38 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="O3" s="10" t="inlineStr">
+      <c r="P3" s="10" t="inlineStr">
         <is>
           <t>This is what a good row looks like: a claim, who it is about, where it came from, and how sure I am.</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="Q3" s="11" t="inlineStr">
         <is>
           <t>IN-000001</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr"/>
-      <c r="R3" s="11" t="inlineStr">
+      <c r="R3" s="11" t="inlineStr"/>
+      <c r="S3" s="11" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="S3" s="12" t="inlineStr"/>
+      <c r="T3" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S3"/>
+  <autoFilter ref="A2:T3"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:T1"/>
   </mergeCells>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="B3:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Or leave it blank — blank is always fine." type="list">
       <formula1>"me,claude,broker,news_alert,other"</formula1>
     </dataValidation>
@@ -1761,9 +1772,12 @@
       <formula1>"confirmed,high,medium,low,rumour"</formula1>
     </dataValidation>
     <dataValidation sqref="N3:N5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Or leave it blank — blank is always fine." type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Or leave it blank — blank is always fine." type="list">
       <formula1>"operator,brand,location,person,market,industry,unknown"</formula1>
     </dataValidation>
-    <dataValidation sqref="R3:R5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Or leave it blank — blank is always fine." type="list">
+    <dataValidation sqref="S3:S5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Or leave it blank — blank is always fine." type="list">
       <formula1>"new,review,queued,submitted,live,rejected,not_for_csw,duplicate"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5407,7 +5421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5423,10 +5437,11 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -5502,22 +5517,27 @@
           <t>confidence</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>» event_id</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="P2" s="8" t="inlineStr">
         <is>
           <t>» op_id</t>
         </is>
       </c>
-      <c r="P2" s="8" t="inlineStr">
+      <c r="Q2" s="8" t="inlineStr">
         <is>
           <t>» from_csw</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="inlineStr">
+      <c r="R2" s="8" t="inlineStr">
         <is>
           <t>» csw_status</t>
         </is>
@@ -5575,18 +5595,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr"/>
+      <c r="O3" s="11" t="inlineStr">
         <is>
           <t>EV-0001</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr"/>
-      <c r="P3" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P3" s="11" t="inlineStr"/>
       <c r="Q3" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -5642,18 +5663,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr"/>
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>EV-0002</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr"/>
-      <c r="P4" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P4" s="11" t="inlineStr"/>
       <c r="Q4" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R4" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -5711,18 +5733,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr"/>
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>EV-0003</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr"/>
-      <c r="P5" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P5" s="11" t="inlineStr"/>
       <c r="Q5" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -5778,18 +5801,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr"/>
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>EV-0004</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R6" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -5845,18 +5869,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr"/>
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>EV-0005</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R7" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -5912,18 +5937,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr"/>
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>EV-0006</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R8" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -5979,18 +6005,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr"/>
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>EV-0007</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R9" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -6046,18 +6073,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr"/>
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>EV-0008</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R10" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -6111,18 +6139,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr"/>
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>EV-0009</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R11" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -6176,18 +6205,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N12" s="9" t="inlineStr"/>
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>EV-0010</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R12" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -6241,18 +6271,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N13" s="9" t="inlineStr"/>
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>EV-0011</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R13" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -6306,18 +6337,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr"/>
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>EV-0012</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R14" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -6371,18 +6403,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr"/>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>EV-0013</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R15" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -6436,18 +6469,19 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr"/>
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>EV-0014</t>
         </is>
       </c>
-      <c r="O16" s="11" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R16" s="11" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -6501,33 +6535,37 @@
           <t>high</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N17" s="9" t="inlineStr"/>
+      <c r="O17" s="11" t="inlineStr">
         <is>
           <t>EV-0015</t>
         </is>
       </c>
-      <c r="O17" s="11" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="11" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R17" s="11" t="inlineStr">
+        <is>
           <t>live</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q17"/>
+  <autoFilter ref="A2:R17"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="M3:M5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Or leave it blank — blank is always fine." type="list">
       <formula1>"confirmed,high,medium,low,rumour"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q3:Q5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Or leave it blank — blank is always fine." type="list">
+    <dataValidation sqref="N3:N5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Or leave it blank — blank is always fine." type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3:R5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Or leave it blank — blank is always fine." type="list">
       <formula1>"new,review,queued,submitted,live,rejected,not_for_csw,duplicate"</formula1>
     </dataValidation>
   </dataValidations>
